--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_47.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3321436.496807546</v>
+        <v>3314379.1492738</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9956801.353979923</v>
+        <v>9946557.879232444</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9956801.353979923</v>
+        <v>9946557.879232444</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12666525.30425547</v>
+        <v>12666642.52634859</v>
       </c>
     </row>
   </sheetData>
@@ -669,13 +669,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>172.1723636724307</v>
+        <v>22.09120398974605</v>
       </c>
       <c r="H2" t="n">
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>193.793770693974</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>421</v>
       </c>
       <c r="S3" t="n">
-        <v>66.5639999646113</v>
+        <v>260.3577706585853</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.99931295557451</v>
+        <v>100.3331446583043</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
@@ -903,7 +903,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>23.2234604107417</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
         <v>3.75737228701621</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>216.3725645856306</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
@@ -1027,16 +1027,16 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>69.30912705343806</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W6" t="n">
         <v>421</v>
       </c>
       <c r="X6" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1182,7 +1182,7 @@
         <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>355.0905731139785</v>
+        <v>358.9713731139785</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,13 +1255,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="S9" t="n">
-        <v>260.3577706585853</v>
+        <v>422</v>
       </c>
       <c r="T9" t="n">
-        <v>5.357765217513816</v>
+        <v>59.84192176744787</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>144.8481678023229</v>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>62.67776252544257</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1495,10 +1495,10 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T12" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U12" t="n">
         <v>50.21035976018675</v>
@@ -1513,7 +1513,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1620,10 +1620,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H14" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1699,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>195.5513766340942</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1741,10 +1741,10 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>145.050905435271</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X15" t="n">
         <v>69.86273944538755</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U17" t="n">
-        <v>299.2212965486107</v>
+        <v>307.0674879340252</v>
       </c>
       <c r="V17" t="n">
         <v>279.8510241668239</v>
@@ -1921,7 +1921,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>73.77767497096173</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1972,16 +1972,16 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T18" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U18" t="n">
-        <v>50.21035976018675</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V18" t="n">
         <v>64.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>82.37314290982852</v>
+        <v>145.0509054352711</v>
       </c>
       <c r="X18" t="n">
         <v>69.86273944538755</v>
@@ -2091,10 +2091,10 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>53.75737228701621</v>
+        <v>61.60356367243072</v>
       </c>
       <c r="H20" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2161,16 +2161,16 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>70.00566530352997</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>86.93822665041533</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>61.97505008894191</v>
+        <v>65.85585008894192</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2398,22 +2398,22 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>64.74007562773993</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>22.47211154361466</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>197.2737972923793</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>148.8135591877373</v>
+        <v>152.6943591877374</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2629,16 +2629,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>34.55655664632661</v>
+        <v>97.23431917176927</v>
       </c>
       <c r="C27" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>64.74007562773993</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>7.846191385414608</v>
       </c>
       <c r="S29" t="n">
         <v>144.8481678023229</v>
@@ -2847,7 +2847,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>283.8164155522384</v>
+        <v>279.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>288.3734759809475</v>
@@ -2881,13 +2881,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>392.8251739264733</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S30" t="n">
         <v>116.5639999646113</v>
@@ -2935,7 +2935,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>49.39139276613435</v>
+        <v>136.3296194165497</v>
       </c>
     </row>
     <row r="31">
@@ -3039,10 +3039,10 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>58.00965870352741</v>
+        <v>65.85585008894192</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>107.5980768338923</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
         <v>11.09991244551929</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3148,10 +3148,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>197.2737972923793</v>
+        <v>436.8722947273425</v>
       </c>
       <c r="S33" t="n">
         <v>116.5639999646113</v>
@@ -3270,7 +3270,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E35" t="n">
-        <v>58.32868099228319</v>
+        <v>54.36328960686865</v>
       </c>
       <c r="F35" t="n">
         <v>54.88962870801186</v>
@@ -3318,7 +3318,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U35" t="n">
-        <v>299.2212965486107</v>
+        <v>307.0674879340252</v>
       </c>
       <c r="V35" t="n">
         <v>279.8510241668239</v>
@@ -3349,10 +3349,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>197.2737972923793</v>
+        <v>219.745908835994</v>
       </c>
       <c r="S36" t="n">
         <v>116.5639999646113</v>
@@ -3513,7 +3513,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>57.72276367243072</v>
+        <v>61.60356367243072</v>
       </c>
       <c r="H38" t="n">
         <v>58.00965870352741</v>
@@ -3586,10 +3586,10 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>73.04152018756569</v>
+        <v>239.5984974349632</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>197.2737972923793</v>
@@ -3750,7 +3750,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>53.75737228701621</v>
+        <v>61.60356367243072</v>
       </c>
       <c r="H41" t="n">
         <v>58.00965870352741</v>
@@ -3798,7 +3798,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>242.2818334606677</v>
@@ -3817,10 +3817,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>11.09991244551929</v>
+        <v>206.6512890796135</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>262.0138729201192</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>230.1079332804208</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>55.35776521751382</v>
@@ -4312,10 +4312,10 @@
         <v>215.6820428039981</v>
       </c>
       <c r="G2" t="n">
-        <v>41.77056434699738</v>
+        <v>193.3676953396081</v>
       </c>
       <c r="H2" t="n">
-        <v>33.68</v>
+        <v>185.2771309926108</v>
       </c>
       <c r="I2" t="n">
         <v>33.68</v>
@@ -4330,13 +4330,13 @@
         <v>433.6300000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>433.6300000000001</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>433.6300000000001</v>
+        <v>1267.21</v>
       </c>
       <c r="O2" t="n">
-        <v>850.4200000000001</v>
+        <v>1267.21</v>
       </c>
       <c r="P2" t="n">
         <v>1267.21</v>
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>448.7508652376995</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="C3" t="n">
-        <v>448.7508652376995</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="D3" t="n">
-        <v>448.7508652376995</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="E3" t="n">
         <v>252.9995817084329</v>
@@ -4427,25 +4427,25 @@
         <v>589.0323546205764</v>
       </c>
       <c r="S3" t="n">
-        <v>521.7959910199589</v>
+        <v>326.0447074906922</v>
       </c>
       <c r="T3" t="n">
-        <v>516.3841069618642</v>
+        <v>320.6328234325975</v>
       </c>
       <c r="U3" t="n">
-        <v>516.1716223556149</v>
+        <v>320.4203388263483</v>
       </c>
       <c r="V3" t="n">
-        <v>501.5143827682208</v>
+        <v>305.7630992389542</v>
       </c>
       <c r="W3" t="n">
-        <v>468.8142384148587</v>
+        <v>273.062954885592</v>
       </c>
       <c r="X3" t="n">
-        <v>448.7508652376995</v>
+        <v>252.9995817084329</v>
       </c>
       <c r="Y3" t="n">
-        <v>448.7508652376995</v>
+        <v>252.9995817084329</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>280.2311926382866</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="C4" t="n">
-        <v>406.2331984567224</v>
+        <v>173.4740175767899</v>
       </c>
       <c r="D4" t="n">
-        <v>519.5523425817225</v>
+        <v>286.79316170179</v>
       </c>
       <c r="E4" t="n">
-        <v>637.3812467931356</v>
+        <v>404.6220659132031</v>
       </c>
       <c r="F4" t="n">
-        <v>761.7422193850711</v>
+        <v>528.9830385051386</v>
       </c>
       <c r="G4" t="n">
-        <v>915.1487852719563</v>
+        <v>682.3896043920238</v>
       </c>
       <c r="H4" t="n">
-        <v>1084.665370431354</v>
+        <v>851.9061895514213</v>
       </c>
       <c r="I4" t="n">
-        <v>1305.798249367437</v>
+        <v>1073.039068487504</v>
       </c>
       <c r="J4" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K4" t="n">
         <v>1544.487243076824</v>
@@ -4506,25 +4506,25 @@
         <v>33.68</v>
       </c>
       <c r="S4" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="U4" t="n">
-        <v>280.2311926382866</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="V4" t="n">
-        <v>280.2311926382866</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="W4" t="n">
-        <v>280.2311926382866</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="X4" t="n">
-        <v>280.2311926382866</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="Y4" t="n">
-        <v>280.2311926382866</v>
+        <v>70.93025509417312</v>
       </c>
     </row>
     <row r="5">
@@ -4534,16 +4534,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>285.4463380542246</v>
+        <v>266.9273161322752</v>
       </c>
       <c r="C5" t="n">
-        <v>235.472016596655</v>
+        <v>216.9529946747056</v>
       </c>
       <c r="D5" t="n">
-        <v>225.028424940241</v>
+        <v>206.5094030182917</v>
       </c>
       <c r="E5" t="n">
-        <v>220.6210617009798</v>
+        <v>202.1020397790304</v>
       </c>
       <c r="F5" t="n">
         <v>197.1630208820488</v>
@@ -4573,10 +4573,10 @@
         <v>1258.569113037656</v>
       </c>
       <c r="O5" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="P5" t="n">
-        <v>1267.21</v>
+        <v>1684</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
@@ -4661,22 +4661,22 @@
         <v>1189.112420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>970.554274322444</v>
+        <v>1040.351008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>903.3179107218266</v>
+        <v>973.1146453614743</v>
       </c>
       <c r="T6" t="n">
-        <v>897.9060266637318</v>
+        <v>967.7027613033796</v>
       </c>
       <c r="U6" t="n">
         <v>897.6935420574825</v>
       </c>
       <c r="V6" t="n">
-        <v>883.0363024700885</v>
+        <v>478.9958984296844</v>
       </c>
       <c r="W6" t="n">
-        <v>457.7837772175632</v>
+        <v>53.74337317715914</v>
       </c>
       <c r="X6" t="n">
         <v>33.68</v>
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115.3301851396645</v>
+        <v>115.4101851396645</v>
       </c>
       <c r="C8" t="n">
-        <v>65.35586368209485</v>
+        <v>65.43586368209485</v>
       </c>
       <c r="D8" t="n">
-        <v>54.91227202568093</v>
+        <v>54.99227202568093</v>
       </c>
       <c r="E8" t="n">
-        <v>50.50490878641967</v>
+        <v>50.58490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>45.565889889438</v>
+        <v>45.645889889438</v>
       </c>
       <c r="G8" t="n">
-        <v>41.77056434699738</v>
+        <v>41.85056434699738</v>
       </c>
       <c r="H8" t="n">
-        <v>33.68</v>
+        <v>33.76</v>
       </c>
       <c r="I8" t="n">
-        <v>33.68</v>
+        <v>33.76</v>
       </c>
       <c r="J8" t="n">
-        <v>424.9891130376557</v>
+        <v>425.0691130376557</v>
       </c>
       <c r="K8" t="n">
-        <v>424.9891130376557</v>
+        <v>842.8491130376557</v>
       </c>
       <c r="L8" t="n">
-        <v>424.9891130376557</v>
+        <v>842.8491130376557</v>
       </c>
       <c r="M8" t="n">
-        <v>841.7791130376559</v>
+        <v>1260.629113037656</v>
       </c>
       <c r="N8" t="n">
-        <v>1258.569113037656</v>
+        <v>1260.629113037656</v>
       </c>
       <c r="O8" t="n">
-        <v>1267.21</v>
+        <v>1678.409113037656</v>
       </c>
       <c r="P8" t="n">
-        <v>1267.21</v>
+        <v>1678.409113037656</v>
       </c>
       <c r="Q8" t="n">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="R8" t="n">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="S8" t="n">
-        <v>1588.193769896644</v>
+        <v>1592.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1229.516423316867</v>
+        <v>1229.596423316867</v>
       </c>
       <c r="U8" t="n">
-        <v>977.7777399344324</v>
+        <v>977.8577399344323</v>
       </c>
       <c r="V8" t="n">
-        <v>745.6049882507718</v>
+        <v>745.6849882507718</v>
       </c>
       <c r="W8" t="n">
-        <v>504.8236993811278</v>
+        <v>504.9036993811278</v>
       </c>
       <c r="X8" t="n">
-        <v>310.5996251784331</v>
+        <v>310.6796251784331</v>
       </c>
       <c r="Y8" t="n">
-        <v>198.1577739836791</v>
+        <v>198.2377739836791</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>252.9995817084329</v>
+        <v>33.76</v>
       </c>
       <c r="C9" t="n">
-        <v>252.9995817084329</v>
+        <v>33.76</v>
       </c>
       <c r="D9" t="n">
-        <v>252.9995817084329</v>
+        <v>33.76</v>
       </c>
       <c r="E9" t="n">
-        <v>252.9995817084329</v>
+        <v>33.76</v>
       </c>
       <c r="F9" t="n">
-        <v>252.9995817084329</v>
+        <v>33.76</v>
       </c>
       <c r="G9" t="n">
-        <v>252.9995817084329</v>
+        <v>33.76</v>
       </c>
       <c r="H9" t="n">
-        <v>252.9995817084329</v>
+        <v>33.76</v>
       </c>
       <c r="I9" t="n">
-        <v>33.68</v>
+        <v>33.76</v>
       </c>
       <c r="J9" t="n">
-        <v>157.636520175299</v>
+        <v>157.7165201752989</v>
       </c>
       <c r="K9" t="n">
-        <v>346.8293362696824</v>
+        <v>346.9093362696823</v>
       </c>
       <c r="L9" t="n">
-        <v>618.1797978648824</v>
+        <v>618.2597978648824</v>
       </c>
       <c r="M9" t="n">
-        <v>704.2603396077417</v>
+        <v>704.3403396077417</v>
       </c>
       <c r="N9" t="n">
-        <v>837.54062421531</v>
+        <v>837.62062421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1076.583075899029</v>
+        <v>1076.663075899029</v>
       </c>
       <c r="P9" t="n">
-        <v>1189.112420368536</v>
+        <v>1189.192420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1014.284879873102</v>
+        <v>1014.364879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>589.0323546205764</v>
+        <v>588.1022536104756</v>
       </c>
       <c r="S9" t="n">
-        <v>326.0447074906922</v>
+        <v>161.8396273478493</v>
       </c>
       <c r="T9" t="n">
-        <v>320.6328234325975</v>
+        <v>101.3932417241646</v>
       </c>
       <c r="U9" t="n">
-        <v>320.4203388263483</v>
+        <v>101.1807571179154</v>
       </c>
       <c r="V9" t="n">
-        <v>305.7630992389542</v>
+        <v>86.52351753052127</v>
       </c>
       <c r="W9" t="n">
-        <v>273.062954885592</v>
+        <v>53.82337317715914</v>
       </c>
       <c r="X9" t="n">
-        <v>252.9995817084329</v>
+        <v>33.76</v>
       </c>
       <c r="Y9" t="n">
-        <v>252.9995817084329</v>
+        <v>33.76</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>518.9201863476736</v>
+        <v>519.000186347674</v>
       </c>
       <c r="C10" t="n">
-        <v>644.9221921661094</v>
+        <v>645.0021921661098</v>
       </c>
       <c r="D10" t="n">
-        <v>758.2413362911095</v>
+        <v>758.3213362911099</v>
       </c>
       <c r="E10" t="n">
-        <v>876.0702405025226</v>
+        <v>876.1502405025229</v>
       </c>
       <c r="F10" t="n">
-        <v>1000.431213094458</v>
+        <v>1000.511213094458</v>
       </c>
       <c r="G10" t="n">
-        <v>1153.837778981343</v>
+        <v>1153.917778981344</v>
       </c>
       <c r="H10" t="n">
-        <v>1323.354364140741</v>
+        <v>1323.434364140741</v>
       </c>
       <c r="I10" t="n">
-        <v>1544.487243076824</v>
+        <v>1544.567243076824</v>
       </c>
       <c r="J10" t="n">
-        <v>1544.487243076824</v>
+        <v>1544.567243076824</v>
       </c>
       <c r="K10" t="n">
-        <v>1544.487243076824</v>
+        <v>1544.567243076824</v>
       </c>
       <c r="L10" t="n">
-        <v>1520.701760089168</v>
+        <v>1520.781760089169</v>
       </c>
       <c r="M10" t="n">
-        <v>1398.85164756134</v>
+        <v>1398.93164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1225.937430115193</v>
+        <v>1226.017430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>983.0631229646733</v>
+        <v>983.1431229646735</v>
       </c>
       <c r="P10" t="n">
-        <v>692.7117115219688</v>
+        <v>692.7917115219689</v>
       </c>
       <c r="Q10" t="n">
-        <v>363.5811393749001</v>
+        <v>363.6611393749001</v>
       </c>
       <c r="R10" t="n">
-        <v>33.68</v>
+        <v>33.76</v>
       </c>
       <c r="S10" t="n">
-        <v>33.68</v>
+        <v>33.76</v>
       </c>
       <c r="T10" t="n">
-        <v>33.68</v>
+        <v>33.76</v>
       </c>
       <c r="U10" t="n">
-        <v>33.68</v>
+        <v>33.76</v>
       </c>
       <c r="V10" t="n">
-        <v>33.68</v>
+        <v>33.76</v>
       </c>
       <c r="W10" t="n">
-        <v>144.7227569781557</v>
+        <v>144.8027569781561</v>
       </c>
       <c r="X10" t="n">
-        <v>295.7535480023492</v>
+        <v>295.8335480023496</v>
       </c>
       <c r="Y10" t="n">
-        <v>407.1628486813815</v>
+        <v>407.2428486813819</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C11" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D11" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E11" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F11" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H11" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I11" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J11" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>733.1420762183976</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>1243.990904947333</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N11" t="n">
-        <v>1797.400904947332</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O11" t="n">
-        <v>1797.400904947332</v>
+        <v>2055.757941766591</v>
       </c>
       <c r="P11" t="n">
-        <v>1797.400904947332</v>
+        <v>2240</v>
       </c>
       <c r="Q11" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R11" t="n">
-        <v>2231.994554156147</v>
+        <v>2240</v>
       </c>
       <c r="S11" t="n">
-        <v>2085.68327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>1846.617029377474</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X11" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y11" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.93203277325181</v>
+        <v>119.3229040110726</v>
       </c>
       <c r="C12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="E12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="F12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="G12" t="n">
-        <v>44.72</v>
+        <v>108.1108712378208</v>
       </c>
       <c r="H12" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I12" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J12" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K12" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L12" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M12" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N12" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O12" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P12" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>529.6091908160197</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T12" t="n">
-        <v>473.6922562528744</v>
+        <v>473.7722562528746</v>
       </c>
       <c r="U12" t="n">
-        <v>422.9747211415747</v>
+        <v>423.0547211415748</v>
       </c>
       <c r="V12" t="n">
-        <v>357.8124310491301</v>
+        <v>357.8924310491302</v>
       </c>
       <c r="W12" t="n">
-        <v>274.6072361907174</v>
+        <v>274.6872361907176</v>
       </c>
       <c r="X12" t="n">
-        <v>204.0388125085078</v>
+        <v>204.1188125085079</v>
       </c>
       <c r="Y12" t="n">
-        <v>90.8376455473191</v>
+        <v>154.2285167851399</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C13" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D13" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E13" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F13" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G13" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H13" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I13" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J13" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K13" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L13" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M13" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N13" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O13" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P13" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q13" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R13" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S13" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>175.5848964865977</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U13" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V13" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W13" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X13" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y13" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>107.3210606959009</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I14" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J14" t="n">
-        <v>436.0291130376557</v>
+        <v>44.8</v>
       </c>
       <c r="K14" t="n">
-        <v>989.4391130376558</v>
+        <v>44.8</v>
       </c>
       <c r="L14" t="n">
-        <v>989.4391130376558</v>
+        <v>181.7520762183974</v>
       </c>
       <c r="M14" t="n">
-        <v>1500.287941766591</v>
+        <v>692.6009049473324</v>
       </c>
       <c r="N14" t="n">
-        <v>2053.697941766591</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="O14" t="n">
-        <v>2236</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>2236</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q14" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R14" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S14" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55.93203277325181</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="F15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="G15" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="H15" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="I15" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J15" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K15" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L15" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M15" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N15" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O15" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P15" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S15" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V15" t="n">
-        <v>357.8124310491301</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W15" t="n">
-        <v>211.2963649528968</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X15" t="n">
-        <v>140.7279412706871</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y15" t="n">
-        <v>90.8376455473191</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>877.7566123122328</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C16" t="n">
-        <v>954.2586181306687</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D16" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E16" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F16" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G16" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H16" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I16" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J16" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K16" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L16" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M16" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N16" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O16" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P16" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q16" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R16" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S16" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U16" t="n">
-        <v>380.3468717970915</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V16" t="n">
-        <v>529.6682646830375</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W16" t="n">
-        <v>652.0591829427149</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X16" t="n">
-        <v>753.5899739669084</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y16" t="n">
-        <v>815.4992746459407</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C17" t="n">
-        <v>332.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D17" t="n">
-        <v>271.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E17" t="n">
-        <v>217.0655061454243</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F17" t="n">
-        <v>161.6214367433921</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G17" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H17" t="n">
-        <v>48.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I17" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J17" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>989.4391130376558</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>1171.741171271065</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M17" t="n">
-        <v>1682.59</v>
+        <v>692.6009049473324</v>
       </c>
       <c r="N17" t="n">
-        <v>1682.59</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="O17" t="n">
-        <v>1682.59</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>2236</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q17" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R17" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S17" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V17" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W17" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X17" t="n">
-        <v>729.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y17" t="n">
-        <v>566.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119.2429040110725</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="D18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J18" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K18" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L18" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M18" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N18" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O18" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P18" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S18" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T18" t="n">
-        <v>473.6922562528744</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U18" t="n">
-        <v>422.9747211415747</v>
+        <v>423.0547211415749</v>
       </c>
       <c r="V18" t="n">
-        <v>357.8124310491301</v>
+        <v>357.8924310491303</v>
       </c>
       <c r="W18" t="n">
-        <v>274.6072361907174</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X18" t="n">
-        <v>204.0388125085078</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y18" t="n">
-        <v>154.1485167851397</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C19" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D19" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E19" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F19" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G19" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H19" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I19" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J19" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K19" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L19" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M19" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N19" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O19" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P19" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q19" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R19" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S19" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
-        <v>175.5848964865977</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>372.6360891248843</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H20" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I20" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J20" t="n">
-        <v>179.7320762183976</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>733.1420762183976</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>733.1420762183976</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="M20" t="n">
-        <v>1243.990904947333</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="N20" t="n">
-        <v>1797.400904947332</v>
+        <v>1685.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1797.400904947332</v>
+        <v>2240</v>
       </c>
       <c r="P20" t="n">
-        <v>1797.400904947332</v>
+        <v>2240</v>
       </c>
       <c r="Q20" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R20" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S20" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y20" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>472.7782575464261</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C21" t="n">
-        <v>461.5662247731743</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D21" t="n">
-        <v>390.8534315372855</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E21" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="F21" t="n">
-        <v>44.72</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="G21" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H21" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I21" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J21" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K21" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L21" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M21" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N21" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O21" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P21" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T21" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U21" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V21" t="n">
-        <v>711.3477845844836</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W21" t="n">
-        <v>628.142589726071</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X21" t="n">
-        <v>557.5741660438614</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y21" t="n">
-        <v>507.6838703204934</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>877.7566123122328</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C22" t="n">
-        <v>954.2586181306687</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D22" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E22" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F22" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G22" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H22" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I22" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J22" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K22" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L22" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M22" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N22" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O22" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P22" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q22" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R22" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S22" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T22" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U22" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V22" t="n">
-        <v>529.6682646830375</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W22" t="n">
-        <v>652.0591829427149</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X22" t="n">
-        <v>753.5899739669084</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y22" t="n">
-        <v>815.4992746459407</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C23" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>107.3210606959009</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H23" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I23" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J23" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>989.4391130376558</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1542.849113037656</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>2053.697941766591</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N23" t="n">
-        <v>2236</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O23" t="n">
-        <v>2236</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="P23" t="n">
-        <v>2236</v>
+        <v>2055.757941766591</v>
       </c>
       <c r="Q23" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>472.7782575464261</v>
+        <v>298.0307170509924</v>
       </c>
       <c r="C24" t="n">
-        <v>461.5662247731743</v>
+        <v>286.8186842777406</v>
       </c>
       <c r="D24" t="n">
-        <v>110.1140157855959</v>
+        <v>286.8186842777406</v>
       </c>
       <c r="E24" t="n">
-        <v>110.1140157855959</v>
+        <v>286.8186842777406</v>
       </c>
       <c r="F24" t="n">
-        <v>44.72</v>
+        <v>286.8186842777406</v>
       </c>
       <c r="G24" t="n">
-        <v>44.72</v>
+        <v>286.8186842777406</v>
       </c>
       <c r="H24" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="I24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J24" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L24" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M24" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N24" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O24" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P24" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.404879873102</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.885958457041</v>
+        <v>826.1384179616076</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>708.3970038559396</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>652.4800692927944</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>601.7625341814946</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>536.60024408905</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>453.3950492306373</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>382.8266255484277</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>332.9363298250597</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C25" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D25" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E25" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F25" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G25" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H25" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I25" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J25" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K25" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L25" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M25" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N25" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O25" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P25" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q25" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R25" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S25" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T25" t="n">
-        <v>175.5848964865977</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V25" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W25" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X25" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y25" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>429.4004881699675</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C26" t="n">
-        <v>328.9211162073474</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D26" t="n">
-        <v>267.972474045883</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E26" t="n">
-        <v>213.0600603015712</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F26" t="n">
-        <v>157.615990899539</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G26" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H26" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I26" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J26" t="n">
-        <v>64.92117127106526</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>618.3311712710653</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>618.3311712710653</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M26" t="n">
-        <v>1129.18</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N26" t="n">
-        <v>1682.59</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O26" t="n">
-        <v>1682.59</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P26" t="n">
-        <v>2236</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q26" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R26" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S26" t="n">
-        <v>2085.68327354774</v>
+        <v>2085.76327354774</v>
       </c>
       <c r="T26" t="n">
-        <v>1846.617029377474</v>
+        <v>1846.697029377473</v>
       </c>
       <c r="U26" t="n">
-        <v>1544.373295489988</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V26" t="n">
-        <v>1261.695493301277</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W26" t="n">
-        <v>970.4091539265823</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X26" t="n">
-        <v>725.6800292188371</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y26" t="n">
-        <v>562.7331275190327</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>472.7782575464261</v>
+        <v>409.5473863086054</v>
       </c>
       <c r="C27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.8</v>
       </c>
       <c r="D27" t="n">
-        <v>110.1140157855959</v>
+        <v>44.8</v>
       </c>
       <c r="E27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J27" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L27" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M27" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N27" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O27" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P27" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S27" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T27" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U27" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V27" t="n">
-        <v>711.3477845844836</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W27" t="n">
-        <v>628.142589726071</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X27" t="n">
-        <v>557.5741660438614</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y27" t="n">
-        <v>507.6838703204934</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>877.7566123122328</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C28" t="n">
-        <v>954.2586181306687</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D28" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E28" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F28" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G28" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H28" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I28" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J28" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K28" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L28" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M28" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N28" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O28" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P28" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q28" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R28" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S28" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T28" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U28" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V28" t="n">
-        <v>529.6682646830375</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W28" t="n">
-        <v>652.0591829427149</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X28" t="n">
-        <v>753.5899739669084</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y28" t="n">
-        <v>815.4992746459407</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>429.4004881699675</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C29" t="n">
-        <v>328.9211162073474</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D29" t="n">
-        <v>267.972474045883</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E29" t="n">
-        <v>213.0600603015712</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F29" t="n">
-        <v>157.615990899539</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H29" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I29" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J29" t="n">
-        <v>179.7320762183977</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>179.7320762183977</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>179.7320762183977</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M29" t="n">
-        <v>690.5809049473327</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N29" t="n">
-        <v>1243.990904947333</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O29" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q29" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R29" t="n">
-        <v>2236</v>
+        <v>2232.074554156147</v>
       </c>
       <c r="S29" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.76327354774</v>
       </c>
       <c r="T29" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.697029377473</v>
       </c>
       <c r="U29" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V29" t="n">
-        <v>1261.695493301277</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W29" t="n">
-        <v>970.4091539265823</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X29" t="n">
-        <v>725.6800292188371</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y29" t="n">
-        <v>562.7331275190327</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>275.2516144816847</v>
+        <v>385.0418669904512</v>
       </c>
       <c r="C30" t="n">
-        <v>264.0395817084329</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="D30" t="n">
-        <v>264.0395817084329</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="E30" t="n">
-        <v>264.0395817084329</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="F30" t="n">
-        <v>264.0395817084329</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="G30" t="n">
-        <v>264.0395817084329</v>
+        <v>44.8</v>
       </c>
       <c r="H30" t="n">
-        <v>264.0395817084329</v>
+        <v>44.8</v>
       </c>
       <c r="I30" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J30" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K30" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L30" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M30" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N30" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O30" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P30" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>803.3593153922999</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>685.6179012866319</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T30" t="n">
-        <v>629.7009667234867</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U30" t="n">
-        <v>578.9834316121869</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V30" t="n">
-        <v>513.8211415197422</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W30" t="n">
-        <v>430.6159466613296</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X30" t="n">
-        <v>360.0475229791199</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y30" t="n">
-        <v>310.1572272557519</v>
+        <v>419.9474797645184</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C31" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D31" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E31" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F31" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G31" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H31" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I31" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J31" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K31" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L31" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M31" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N31" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O31" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P31" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q31" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R31" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S31" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T31" t="n">
-        <v>175.5848964865977</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U31" t="n">
-        <v>372.6360891248843</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W31" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X31" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y31" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C32" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D32" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E32" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F32" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H32" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I32" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J32" t="n">
-        <v>44.72</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>44.72</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>44.72</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>555.568828728935</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N32" t="n">
-        <v>1108.978828728935</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1662.388828728935</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P32" t="n">
-        <v>2215.798828728935</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q32" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R32" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S32" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T32" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U32" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V32" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W32" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X32" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y32" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>398.9989442256527</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C33" t="n">
-        <v>387.7869114524009</v>
+        <v>44.8</v>
       </c>
       <c r="D33" t="n">
-        <v>387.7869114524009</v>
+        <v>44.8</v>
       </c>
       <c r="E33" t="n">
-        <v>387.7869114524009</v>
+        <v>44.8</v>
       </c>
       <c r="F33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J33" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L33" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M33" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N33" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O33" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P33" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.404879873102</v>
       </c>
       <c r="R33" t="n">
-        <v>1000.885958457041</v>
+        <v>584.119733683867</v>
       </c>
       <c r="S33" t="n">
-        <v>883.1445443513733</v>
+        <v>466.3783195781991</v>
       </c>
       <c r="T33" t="n">
-        <v>827.2276097882281</v>
+        <v>410.4613850150538</v>
       </c>
       <c r="U33" t="n">
-        <v>776.5100746769283</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V33" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W33" t="n">
-        <v>628.142589726071</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X33" t="n">
-        <v>557.5741660438614</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y33" t="n">
-        <v>507.6838703204934</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C34" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D34" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E34" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F34" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G34" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H34" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I34" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J34" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K34" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L34" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M34" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N34" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O34" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P34" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q34" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R34" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S34" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T34" t="n">
-        <v>175.5848964865977</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U34" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V34" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W34" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X34" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y34" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>271.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I35" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J35" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>436.0291130376557</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="L35" t="n">
-        <v>436.0291130376557</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>690.5809049473327</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="N35" t="n">
-        <v>1243.990904947333</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="O35" t="n">
-        <v>1243.990904947333</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q35" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>275.3316144816847</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="D36" t="n">
-        <v>461.5662247731743</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="E36" t="n">
-        <v>387.7869114524009</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="G36" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="H36" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="I36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J36" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K36" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L36" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M36" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N36" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O36" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P36" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.404879873102</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>803.4393153922998</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>685.6979012866318</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>629.7809667234866</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>579.0634316121868</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>513.9011415197422</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>430.6959466613296</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>360.1275229791199</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>310.2372272557519</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J37" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K37" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L37" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M37" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N37" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O37" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P37" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q37" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R37" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S37" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I38" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J38" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>989.4391130376558</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>1542.849113037656</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="M38" t="n">
-        <v>1682.59</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="N38" t="n">
-        <v>1682.59</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="O38" t="n">
-        <v>2236</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P38" t="n">
-        <v>2236</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q38" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>298.0307170509924</v>
       </c>
       <c r="C39" t="n">
-        <v>461.5662247731743</v>
+        <v>286.8186842777406</v>
       </c>
       <c r="D39" t="n">
-        <v>461.5662247731743</v>
+        <v>286.8186842777406</v>
       </c>
       <c r="E39" t="n">
-        <v>387.7869114524009</v>
+        <v>44.8</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J39" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K39" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L39" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M39" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N39" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O39" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P39" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.404879873102</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>826.1384179616076</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>708.3970038559396</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>652.4800692927944</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>601.7625341814946</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>536.60024408905</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>453.3950492306373</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>382.8266255484277</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>332.9363298250597</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F40" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G40" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H40" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I40" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J40" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K40" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L40" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M40" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N40" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O40" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P40" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q40" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R40" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S40" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I41" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="L41" t="n">
-        <v>436.0291130376557</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="M41" t="n">
-        <v>946.8779417665908</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q41" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>407.3842417608302</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C42" t="n">
-        <v>396.1722089875784</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="G42" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="H42" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="I42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J42" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K42" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L42" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M42" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N42" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O42" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>935.4919426714454</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>817.7505285657774</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T42" t="n">
-        <v>761.8335940026321</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U42" t="n">
-        <v>711.1160588913324</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V42" t="n">
-        <v>645.9537687988877</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W42" t="n">
-        <v>562.7485739404751</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X42" t="n">
-        <v>492.1801502582655</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y42" t="n">
-        <v>442.2898545348975</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877.7566123122328</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.486666467082</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.347639059017</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.254204945903</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.2707901053</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.903669041383</v>
       </c>
       <c r="J43" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K43" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L43" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M43" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N43" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O43" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P43" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q43" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R43" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S43" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>380.3468717970915</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>529.6682646830375</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W43" t="n">
-        <v>652.0591829427149</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X43" t="n">
-        <v>753.5899739669084</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y43" t="n">
-        <v>815.4992746459407</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I44" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J44" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>436.0291130376557</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>436.0291130376557</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="M44" t="n">
-        <v>946.8779417665908</v>
+        <v>1685.6</v>
       </c>
       <c r="N44" t="n">
-        <v>1500.287941766591</v>
+        <v>2240</v>
       </c>
       <c r="O44" t="n">
-        <v>2053.697941766591</v>
+        <v>2240</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="Q44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>275.3316144816847</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="H45" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="I45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J45" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K45" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L45" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M45" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N45" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O45" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P45" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>466.2983195781991</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T45" t="n">
-        <v>410.3813850150538</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U45" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V45" t="n">
-        <v>294.5015598113094</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W45" t="n">
-        <v>211.2963649528968</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K46" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L46" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M46" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N46" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O46" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P46" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q46" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R46" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S46" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U46" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V46" t="n">
-        <v>529.6682646830375</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W46" t="n">
-        <v>652.0591829427149</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
   </sheetData>
@@ -7973,16 +7973,16 @@
         <v>403.9898989898991</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>965.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>898.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>491.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P2" t="n">
-        <v>421.2870600406814</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
         <v>593.8226843274854</v>
@@ -8216,13 +8216,13 @@
         <v>898.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>78.97603822292498</v>
+        <v>491.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2870600406814136</v>
+        <v>9.015228689513952</v>
       </c>
       <c r="Q5" t="n">
-        <v>593.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,25 +8441,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>965.2621276423173</v>
+        <v>966.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>898.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>78.97603822292498</v>
+        <v>492.2478695740924</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>593.8226843274854</v>
+        <v>182.510448935914</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8681,22 +8681,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>186.3901491653373</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>254.3913627391524</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,25 +9152,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>803.3447457328998</v>
       </c>
       <c r="N17" t="n">
-        <v>477.2489580698352</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>171.4188408091283</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
-        <v>1036.248958069835</v>
+        <v>619.360965102506</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,25 +9626,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>661.3924512348951</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O23" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q23" t="n">
-        <v>172.8226843274854</v>
+        <v>358.9257734521414</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,10 +9860,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>55.44822975121687</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9872,16 +9872,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>373.3215697566601</v>
       </c>
       <c r="P26" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>171.4188408091284</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10109,10 +10109,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>373.3215697566601</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10346,16 +10346,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>629.2478695740924</v>
+        <v>373.3215697566601</v>
       </c>
       <c r="P32" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,22 +10574,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>801.385149773304</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>329.330487664675</v>
       </c>
       <c r="P35" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10811,25 +10811,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>685.4145387153924</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>629.2478695740924</v>
+        <v>329.330487664675</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,19 +11048,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>259.0826180905825</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11285,22 +11285,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>686.3741346749882</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>184.4305532057413</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>172.8226843274854</v>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2229305.285859985</v>
+        <v>2229352.563435743</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2959971.389505774</v>
+        <v>2960018.667081531</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3684113.187697016</v>
+        <v>3684160.465272774</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4408254.985888258</v>
+        <v>4408302.263464016</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5132396.784079497</v>
+        <v>5132444.061655255</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5856538.582270736</v>
+        <v>5856585.859846494</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6580680.380461975</v>
+        <v>6580727.658037733</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7304822.178653214</v>
+        <v>7304869.456228972</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8028963.976844459</v>
+        <v>8029011.254420217</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8753105.775035705</v>
+        <v>8753153.052611463</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9477247.573226953</v>
+        <v>9477294.85080271</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10201389.3714182</v>
+        <v>10201436.64899396</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10925531.16960945</v>
+        <v>10925578.4471852</v>
       </c>
     </row>
   </sheetData>
@@ -26278,7 +26278,7 @@
         <v>1479768.022390799</v>
       </c>
       <c r="E2" t="n">
-        <v>1479768.022390799</v>
+        <v>1479768.022390798</v>
       </c>
       <c r="F2" t="n">
         <v>1479768.022390799</v>
@@ -26287,7 +26287,7 @@
         <v>1479768.022390799</v>
       </c>
       <c r="H2" t="n">
-        <v>1479768.022390799</v>
+        <v>1479768.022390798</v>
       </c>
       <c r="I2" t="n">
         <v>1479768.022390798</v>
@@ -26311,7 +26311,7 @@
         <v>1479768.022390799</v>
       </c>
       <c r="P2" t="n">
-        <v>1479768.022390799</v>
+        <v>1479768.022390798</v>
       </c>
     </row>
     <row r="3">
@@ -26327,7 +26327,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="E3" t="n">
         <v>328576</v>
@@ -26351,7 +26351,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="M3" t="n">
         <v>48576</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425093</v>
+        <v>567917.5723359545</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724099</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563725.2378061949</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544712.0690347301</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542769.8864290809</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540825.0236843044</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538877.4615810197</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>536927.1806494284</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>534974.1611645631</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533018.3831414287</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531059.8263300107</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529098.4702101595</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527134.2939863529</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525167.2765823142</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523197.3966354961</v>
       </c>
     </row>
     <row r="5">
@@ -26431,43 +26431,43 @@
         <v>59224.39999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>59224.39999999999</v>
+        <v>59285.2</v>
       </c>
       <c r="E5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="F5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="G5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="H5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="I5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="J5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="K5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="L5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="M5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="N5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="O5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="P5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>705996.6631482895</v>
+        <v>704434.0500548441</v>
       </c>
       <c r="C6" t="n">
-        <v>856221.1789118344</v>
+        <v>854658.5658183889</v>
       </c>
       <c r="D6" t="n">
-        <v>858256.4519098733</v>
+        <v>856405.584584604</v>
       </c>
       <c r="E6" t="n">
-        <v>544686.6191642637</v>
+        <v>543007.8033560683</v>
       </c>
       <c r="F6" t="n">
-        <v>875205.5145097676</v>
+        <v>873525.9859617178</v>
       </c>
       <c r="G6" t="n">
-        <v>877151.0909779532</v>
+        <v>875470.8487064944</v>
       </c>
       <c r="H6" t="n">
-        <v>879099.3677952547</v>
+        <v>877418.4108097787</v>
       </c>
       <c r="I6" t="n">
-        <v>881050.364438614</v>
+        <v>879368.69174137</v>
       </c>
       <c r="J6" t="n">
-        <v>454812.1006402391</v>
+        <v>453129.711226235</v>
       </c>
       <c r="K6" t="n">
-        <v>884960.5963924597</v>
+        <v>883277.4892493702</v>
       </c>
       <c r="L6" t="n">
-        <v>886919.8719527182</v>
+        <v>884884.0460607877</v>
       </c>
       <c r="M6" t="n">
-        <v>840305.9478486981</v>
+        <v>838621.4021806393</v>
       </c>
       <c r="N6" t="n">
-        <v>890846.8448835511</v>
+        <v>889161.5784044453</v>
       </c>
       <c r="O6" t="n">
-        <v>612814.5841412896</v>
+        <v>611128.5958084849</v>
       </c>
       <c r="P6" t="n">
-        <v>894785.1869922999</v>
+        <v>893098.4757553024</v>
       </c>
     </row>
   </sheetData>
@@ -26865,43 +26865,43 @@
         <v>421</v>
       </c>
       <c r="D4" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -26972,25 +26972,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -27005,16 +27005,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>350</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27030,7 +27030,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -27039,13 +27039,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27054,7 +27054,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -27066,7 +27066,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -27079,34 +27079,34 @@
         <v>421</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>138</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>138</v>
@@ -27115,10 +27115,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27323,7 +27323,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>138</v>
@@ -27448,13 +27448,13 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>231.5850086145855</v>
+        <v>381.6661682972701</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27521,7 +27521,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>148.8783265279386</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27563,7 +27563,7 @@
         <v>126.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>206.206229306026</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27594,7 +27594,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>376.304804711294</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>276.3689424817532</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27670,7 +27670,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>400</v>
+        <v>381.6661682972701</v>
       </c>
       <c r="C5" t="n">
         <v>400</v>
@@ -27682,7 +27682,7 @@
         <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>381.6661682972701</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
         <v>400</v>
@@ -27797,7 +27797,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>330.9012327067487</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,16 +27806,16 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>330.9012327067487</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>11.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27961,7 +27961,7 @@
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>231.5850086145854</v>
+        <v>227.7042086145854</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,13 +28034,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>126.2737972923793</v>
+        <v>125.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>206.206229306026</v>
+        <v>44.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>345.515843450066</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28128,7 +28128,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>338.5372108267458</v>
+        <v>338.5372108267462</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
         <v>350</v>
@@ -28241,7 +28241,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28274,10 +28274,10 @@
         <v>350</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>350</v>
@@ -28292,7 +28292,7 @@
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -28356,7 +28356,7 @@
         <v>350</v>
       </c>
       <c r="T13" t="n">
-        <v>342.2113306341342</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U13" t="n">
         <v>350</v>
@@ -28399,10 +28399,10 @@
         <v>350</v>
       </c>
       <c r="H14" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28478,10 +28478,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>136.6167105523269</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28520,10 +28520,10 @@
         <v>350</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W15" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="X15" t="n">
         <v>350</v>
@@ -28545,7 +28545,7 @@
         <v>350</v>
       </c>
       <c r="D16" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="E16" t="n">
         <v>350</v>
@@ -28560,7 +28560,7 @@
         <v>350</v>
       </c>
       <c r="I16" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="J16" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28675,7 +28675,7 @@
         <v>350</v>
       </c>
       <c r="U17" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="V17" t="n">
         <v>350</v>
@@ -28700,7 +28700,7 @@
         <v>350</v>
       </c>
       <c r="C18" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -28751,16 +28751,16 @@
         <v>350</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>350</v>
       </c>
       <c r="W18" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="X18" t="n">
         <v>350</v>
@@ -28776,7 +28776,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>350</v>
+        <v>342.2113306341345</v>
       </c>
       <c r="C19" t="n">
         <v>350</v>
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28870,10 +28870,10 @@
         <v>350</v>
       </c>
       <c r="G20" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="H20" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I20" t="n">
         <v>150.0811596826846</v>
@@ -28940,16 +28940,16 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>277.9320215941727</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>252.6980156874615</v>
       </c>
       <c r="G21" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>332.1680871864211</v>
@@ -29040,7 +29040,7 @@
         <v>350</v>
       </c>
       <c r="K22" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="L22" t="n">
         <v>350</v>
@@ -29067,7 +29067,7 @@
         <v>350</v>
       </c>
       <c r="T22" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U22" t="n">
         <v>350</v>
@@ -29110,7 +29110,7 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>346.0346086145855</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29177,22 +29177,22 @@
         <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>274.8961667101369</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>332.1680871864211</v>
+        <v>309.6959756428064</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>350</v>
@@ -29304,10 +29304,10 @@
         <v>350</v>
       </c>
       <c r="T25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U25" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="V25" t="n">
         <v>350</v>
@@ -29380,7 +29380,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>346.0346086145856</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29408,16 +29408,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="C27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>277.9320215941727</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
@@ -29505,7 +29505,7 @@
         <v>350</v>
       </c>
       <c r="H28" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="I28" t="n">
         <v>350</v>
@@ -29541,7 +29541,7 @@
         <v>350</v>
       </c>
       <c r="T28" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U28" t="n">
         <v>350</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282945</v>
+        <v>243.0324074428798</v>
       </c>
       <c r="S29" t="n">
         <v>350</v>
@@ -29626,7 +29626,7 @@
         <v>350</v>
       </c>
       <c r="V29" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="W29" t="n">
         <v>350</v>
@@ -29660,13 +29660,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29693,7 +29693,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
       <c r="S30" t="n">
         <v>350</v>
@@ -29714,7 +29714,7 @@
         <v>350</v>
       </c>
       <c r="Y30" t="n">
-        <v>350</v>
+        <v>263.0617733495847</v>
       </c>
     </row>
     <row r="31">
@@ -29778,7 +29778,7 @@
         <v>350</v>
       </c>
       <c r="T31" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U31" t="n">
         <v>350</v>
@@ -29790,7 +29790,7 @@
         <v>350</v>
       </c>
       <c r="X31" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="Y31" t="n">
         <v>350</v>
@@ -29818,10 +29818,10 @@
         <v>350</v>
       </c>
       <c r="G32" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H32" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="I32" t="n">
         <v>150.0811596826846</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="C33" t="n">
         <v>350</v>
@@ -29894,7 +29894,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>325.7395358750273</v>
@@ -29927,10 +29927,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>350</v>
+        <v>110.4015025650368</v>
       </c>
       <c r="S33" t="n">
         <v>350</v>
@@ -30015,7 +30015,7 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
-        <v>342.2113306341342</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U34" t="n">
         <v>350</v>
@@ -30049,7 +30049,7 @@
         <v>350</v>
       </c>
       <c r="E35" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="F35" t="n">
         <v>350</v>
@@ -30097,7 +30097,7 @@
         <v>350</v>
       </c>
       <c r="U35" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="V35" t="n">
         <v>350</v>
@@ -30128,10 +30128,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>325.7395358750273</v>
@@ -30140,7 +30140,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,10 +30164,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>350</v>
+        <v>327.5278884563853</v>
       </c>
       <c r="S36" t="n">
         <v>350</v>
@@ -30252,10 +30252,10 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="V37" t="n">
         <v>350</v>
@@ -30292,7 +30292,7 @@
         <v>350</v>
       </c>
       <c r="G38" t="n">
-        <v>346.0346086145855</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="H38" t="n">
         <v>350</v>
@@ -30365,10 +30365,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>269.6305770343469</v>
+        <v>103.0735997869494</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>350</v>
@@ -30462,7 +30462,7 @@
         <v>350</v>
       </c>
       <c r="K40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="L40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30529,7 +30529,7 @@
         <v>350</v>
       </c>
       <c r="G41" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="H41" t="n">
         <v>350</v>
@@ -30577,7 +30577,7 @@
         <v>350</v>
       </c>
       <c r="W41" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X41" t="n">
         <v>350</v>
@@ -30596,10 +30596,10 @@
         <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>350</v>
+        <v>154.4486233659058</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
@@ -30614,7 +30614,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>285.25992437226</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30675,7 +30675,7 @@
         <v>350</v>
       </c>
       <c r="C43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="D43" t="n">
         <v>350</v>
@@ -30696,7 +30696,7 @@
         <v>350</v>
       </c>
       <c r="J43" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="K43" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>154.4486233659058</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
@@ -30851,7 +30851,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30878,10 +30878,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S45" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T45" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -30975,7 +30975,7 @@
         <v>350</v>
       </c>
       <c r="X46" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="Y46" t="n">
         <v>350</v>
@@ -34752,16 +34752,16 @@
         <v>403.9898989898991</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="O2" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>421</v>
@@ -34880,7 +34880,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>103.5795580632493</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
@@ -34901,10 +34901,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>241.0999936458454</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -34995,13 +34995,13 @@
         <v>421</v>
       </c>
       <c r="O5" t="n">
+        <v>421</v>
+      </c>
+      <c r="P5" t="n">
         <v>8.728168648832536</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35220,25 +35220,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N8" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8.728168648832536</v>
+        <v>422</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>421</v>
+        <v>9.687764608428543</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35414,7 +35414,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>112.1644009880361</v>
+        <v>112.1644009880365</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35460,22 +35460,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>186.1030891246559</v>
       </c>
       <c r="Q11" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35642,7 +35642,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>132.1867641278765</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U13" t="n">
         <v>199.0416087255421</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O14" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35831,7 +35831,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D16" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857893</v>
       </c>
       <c r="E16" t="n">
         <v>69.01909516304346</v>
@@ -35846,7 +35846,7 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I16" t="n">
-        <v>165.577875014016</v>
+        <v>173.3665443798817</v>
       </c>
       <c r="J16" t="n">
         <v>314.7310511640923</v>
@@ -35931,25 +35931,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>516.0089179080152</v>
+        <v>259.0826180905825</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="P17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36062,7 +36062,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705578</v>
       </c>
       <c r="C19" t="n">
         <v>77.27475335195533</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>559</v>
+        <v>142.1120070326709</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36326,7 +36326,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K22" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
@@ -36405,25 +36405,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>184.1434931650599</v>
+        <v>560</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>186.1030891246559</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36590,10 +36590,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U25" t="n">
-        <v>199.0416087255421</v>
+        <v>191.2529393596764</v>
       </c>
       <c r="V25" t="n">
         <v>150.8296897837838</v>
@@ -36639,10 +36639,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>20.40522350612654</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36651,16 +36651,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>303.0737001825676</v>
       </c>
       <c r="P26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36791,7 +36791,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H28" t="n">
-        <v>113.4402045325156</v>
+        <v>121.2288738983814</v>
       </c>
       <c r="I28" t="n">
         <v>173.3665443798817</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U28" t="n">
         <v>199.0416087255421</v>
@@ -36876,7 +36876,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -36888,10 +36888,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>303.0737001825676</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U31" t="n">
         <v>199.0416087255421</v>
@@ -37076,7 +37076,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X31" t="n">
-        <v>102.5563545698924</v>
+        <v>94.7676852040268</v>
       </c>
       <c r="Y31" t="n">
         <v>62.53464715053764</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -37125,16 +37125,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O32" t="n">
-        <v>559</v>
+        <v>303.0737001825676</v>
       </c>
       <c r="P32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>132.1867641278765</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U34" t="n">
         <v>199.0416087255421</v>
@@ -37353,22 +37353,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>257.1230221309867</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>259.0826180905826</v>
       </c>
       <c r="P35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>443.0293889420883</v>
@@ -37538,10 +37538,10 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U37" t="n">
-        <v>191.2529393596762</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V37" t="n">
         <v>150.8296897837838</v>
@@ -37590,25 +37590,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>141.1524110730751</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>559</v>
+        <v>259.0826180905826</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37748,7 +37748,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37827,19 +37827,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>259.0826180905825</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O41" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37961,7 +37961,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C43" t="n">
-        <v>69.48608398608951</v>
+        <v>77.27475335195533</v>
       </c>
       <c r="D43" t="n">
         <v>64.46378194444452</v>
@@ -37982,7 +37982,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982266</v>
       </c>
       <c r="K43" t="n">
         <v>61.47922619885696</v>
@@ -38064,22 +38064,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>142.1120070326709</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
@@ -38261,7 +38261,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X46" t="n">
-        <v>94.76768520402656</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y46" t="n">
         <v>62.53464715053764</v>
